--- a/outputs/test_predicted.xlsx
+++ b/outputs/test_predicted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,11 +532,56 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>2.180034856666667</v>
+        <v>2.090871641166666</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Zr-acac</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>acac</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.509</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>1.711840532999999</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Cu-acac</t>
         </is>
       </c>
     </row>
